--- a/output/yearly_benthic_cover_iteration_84_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_84_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.13438943390857</v>
+        <v>45.61814364338967</v>
       </c>
       <c r="M2" t="n">
-        <v>101.006068074419</v>
+        <v>99.60797179355185</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.06008414694942</v>
+        <v>88.01996011827684</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93437870997261</v>
+        <v>45.91557340087468</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2288103454604</v>
+        <v>2.228721706626649</v>
       </c>
       <c r="E3" t="n">
-        <v>5.711426439265525</v>
+        <v>5.69849276108581</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429367818201332</v>
+        <v>0.7429072355422166</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9747508005718</v>
+        <v>33.96864292621975</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17509196372612</v>
+        <v>34.17373283494196</v>
       </c>
       <c r="I3" t="n">
-        <v>6.583712929729607</v>
+        <v>6.564292431721612</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643354886375832</v>
+        <v>4.643170222138854</v>
       </c>
       <c r="K3" t="n">
-        <v>11.93991585305057</v>
+        <v>11.98003988172314</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88939235836466</v>
+        <v>48.86876133942145</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7636869213878</v>
+        <v>106.7643746220193</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.14719699410946</v>
+        <v>87.11523581547327</v>
       </c>
       <c r="C4" t="n">
-        <v>42.65944178785145</v>
+        <v>42.64574760885442</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184852964689293</v>
+        <v>2.185167139052318</v>
       </c>
       <c r="E4" t="n">
-        <v>6.515111193580863</v>
+        <v>6.500750130285947</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444991347984563</v>
+        <v>0.7444654809949294</v>
       </c>
       <c r="G4" t="n">
-        <v>33.30468882756184</v>
+        <v>33.30481417212299</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24696020072899</v>
+        <v>34.24541212576675</v>
       </c>
       <c r="I4" t="n">
-        <v>5.497965080259664</v>
+        <v>5.481717511032037</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65311959249035</v>
+        <v>4.652909256218308</v>
       </c>
       <c r="K4" t="n">
-        <v>12.85280300589054</v>
+        <v>12.88476418452671</v>
       </c>
       <c r="L4" t="n">
-        <v>44.3048742915433</v>
+        <v>44.28714675018216</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8171190852853</v>
+        <v>99.81765854356328</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.93058180725136</v>
+        <v>86.01242687101117</v>
       </c>
       <c r="C5" t="n">
-        <v>42.29614319491953</v>
+        <v>42.39373763230405</v>
       </c>
       <c r="D5" t="n">
-        <v>2.125348581414876</v>
+        <v>2.131551301362659</v>
       </c>
       <c r="E5" t="n">
-        <v>7.10263820695392</v>
+        <v>7.103945890053355</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458246614485087</v>
+        <v>0.745785764015135</v>
       </c>
       <c r="G5" t="n">
-        <v>32.39763695685976</v>
+        <v>32.48763846092717</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30793442663139</v>
+        <v>34.30614514469621</v>
       </c>
       <c r="I5" t="n">
-        <v>4.589794839889729</v>
+        <v>4.576199284862048</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661404134053178</v>
+        <v>4.661161025094593</v>
       </c>
       <c r="K5" t="n">
-        <v>14.06941819274864</v>
+        <v>13.98757312898885</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48171736010239</v>
+        <v>43.46641930784509</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84727874777056</v>
+        <v>99.84773006913797</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.69229506079246</v>
+        <v>84.67729348701731</v>
       </c>
       <c r="C6" t="n">
-        <v>41.7706331657584</v>
+        <v>41.7693712663731</v>
       </c>
       <c r="D6" t="n">
-        <v>2.065232283701105</v>
+        <v>2.06644413895934</v>
       </c>
       <c r="E6" t="n">
-        <v>7.540169958841247</v>
+        <v>7.523498235123562</v>
       </c>
       <c r="F6" t="n">
-        <v>0.746949105580184</v>
+        <v>0.7469070128297082</v>
       </c>
       <c r="G6" t="n">
-        <v>31.48125740126484</v>
+        <v>31.49531988430003</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35965885668845</v>
+        <v>34.35772259016657</v>
       </c>
       <c r="I6" t="n">
-        <v>3.830595544840476</v>
+        <v>3.819232795452406</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668431909876149</v>
+        <v>4.668168830185675</v>
       </c>
       <c r="K6" t="n">
-        <v>15.30770493920754</v>
+        <v>15.32270651298269</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79416759392601</v>
+        <v>42.78080557384251</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87250569889196</v>
+        <v>99.8728833531983</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.1912831068129</v>
+        <v>83.17103510118037</v>
       </c>
       <c r="C7" t="n">
-        <v>40.86462395441346</v>
+        <v>40.85635988474411</v>
       </c>
       <c r="D7" t="n">
-        <v>1.992331786570851</v>
+        <v>1.993227126199026</v>
       </c>
       <c r="E7" t="n">
-        <v>7.806718517980863</v>
+        <v>7.788056629626013</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479057109738105</v>
+        <v>0.7478609557382109</v>
       </c>
       <c r="G7" t="n">
-        <v>30.37000258845278</v>
+        <v>30.37939654798363</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40366270479527</v>
+        <v>34.4016039639577</v>
       </c>
       <c r="I7" t="n">
-        <v>3.196251104453017</v>
+        <v>3.186758904311973</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674410693586315</v>
+        <v>4.674130973363818</v>
       </c>
       <c r="K7" t="n">
-        <v>16.80871689318708</v>
+        <v>16.82896489881962</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22025372059834</v>
+        <v>42.20858541656259</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89359456819888</v>
+        <v>99.89391020012631</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.07448293562172</v>
+        <v>87.95245000526972</v>
       </c>
       <c r="C8" t="n">
-        <v>43.1478800614842</v>
+        <v>43.06107440230609</v>
       </c>
       <c r="D8" t="n">
-        <v>1.996608674207623</v>
+        <v>1.997487738837761</v>
       </c>
       <c r="E8" t="n">
-        <v>9.629062742996275</v>
+        <v>9.556130667161185</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749511221015007</v>
+        <v>0.7494595421703107</v>
       </c>
       <c r="G8" t="n">
-        <v>30.86532187268266</v>
+        <v>30.85004143758328</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47751616669031</v>
+        <v>34.4751389398343</v>
       </c>
       <c r="I8" t="n">
-        <v>5.672017126686048</v>
+        <v>5.640069541118432</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684445131343792</v>
+        <v>4.684122138564442</v>
       </c>
       <c r="K8" t="n">
-        <v>11.92551706437828</v>
+        <v>12.04754999473029</v>
       </c>
       <c r="L8" t="n">
-        <v>44.7379406329841</v>
+        <v>44.70377429116871</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81133775884658</v>
+        <v>99.81239868820508</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.22788292338515</v>
+        <v>86.01814909714911</v>
       </c>
       <c r="C9" t="n">
-        <v>42.18168465514918</v>
+        <v>42.00216146945395</v>
       </c>
       <c r="D9" t="n">
-        <v>1.913334868034737</v>
+        <v>1.909848094582238</v>
       </c>
       <c r="E9" t="n">
-        <v>10.01667963087814</v>
+        <v>9.921628389259743</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508832387319098</v>
+        <v>0.7508270561628548</v>
       </c>
       <c r="G9" t="n">
-        <v>29.57800259760761</v>
+        <v>29.49649788170089</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54062898166784</v>
+        <v>34.53804458349133</v>
       </c>
       <c r="I9" t="n">
-        <v>4.735333364390468</v>
+        <v>4.708633990934207</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693020242074434</v>
+        <v>4.692669101017843</v>
       </c>
       <c r="K9" t="n">
-        <v>13.77211707661484</v>
+        <v>13.98185090285089</v>
       </c>
       <c r="L9" t="n">
-        <v>43.88864223693914</v>
+        <v>43.85931902933077</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84244396870318</v>
+        <v>99.84333140163561</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.28896969812924</v>
+        <v>83.83767545157569</v>
       </c>
       <c r="C10" t="n">
-        <v>40.97767229949514</v>
+        <v>40.5523047193176</v>
       </c>
       <c r="D10" t="n">
-        <v>1.82681042349598</v>
+        <v>1.811910827099061</v>
       </c>
       <c r="E10" t="n">
-        <v>10.22242050285136</v>
+        <v>10.06784475797791</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520568600498287</v>
+        <v>0.752000253832344</v>
       </c>
       <c r="G10" t="n">
-        <v>28.24043211369511</v>
+        <v>27.98391349813032</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59461556229211</v>
+        <v>34.59201167628784</v>
       </c>
       <c r="I10" t="n">
-        <v>3.952278860433417</v>
+        <v>3.92999285179607</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700355375311428</v>
+        <v>4.70000158645215</v>
       </c>
       <c r="K10" t="n">
-        <v>15.71103030187078</v>
+        <v>16.16232454842432</v>
       </c>
       <c r="L10" t="n">
-        <v>43.17976036073433</v>
+        <v>43.15457534362101</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86846296210024</v>
+        <v>99.86920461136293</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.22955672309358</v>
+        <v>81.58145663322665</v>
       </c>
       <c r="C11" t="n">
-        <v>39.53123454456129</v>
+        <v>38.90528285921785</v>
       </c>
       <c r="D11" t="n">
-        <v>1.735750115932241</v>
+        <v>1.711650029572799</v>
       </c>
       <c r="E11" t="n">
-        <v>10.26252896826769</v>
+        <v>10.05731143852874</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530622812191543</v>
+        <v>0.7530078750930068</v>
       </c>
       <c r="G11" t="n">
-        <v>26.83274229490991</v>
+        <v>26.43544353853495</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64086493608109</v>
+        <v>34.63836225427833</v>
       </c>
       <c r="I11" t="n">
-        <v>3.29796886906378</v>
+        <v>3.27938227788754</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706639257619713</v>
+        <v>4.706299219331292</v>
       </c>
       <c r="K11" t="n">
-        <v>17.77044327690642</v>
+        <v>18.41854336677335</v>
       </c>
       <c r="L11" t="n">
-        <v>42.58853665463138</v>
+        <v>42.56700730590338</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89021447609909</v>
+        <v>99.89083353189457</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.08875432501233</v>
+        <v>79.29841963376698</v>
       </c>
       <c r="C12" t="n">
-        <v>37.90133249406215</v>
+        <v>37.12984564308756</v>
       </c>
       <c r="D12" t="n">
-        <v>1.641934199259936</v>
+        <v>1.611215314676974</v>
       </c>
       <c r="E12" t="n">
-        <v>10.16642319739346</v>
+        <v>9.923170829498321</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539246647692629</v>
+        <v>0.7538738866994108</v>
       </c>
       <c r="G12" t="n">
-        <v>25.38245386219004</v>
+        <v>24.88428752587734</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68053457938608</v>
+        <v>34.67819878817291</v>
       </c>
       <c r="I12" t="n">
-        <v>2.751454667205654</v>
+        <v>2.735961496970722</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712029154807892</v>
+        <v>4.711711791871317</v>
       </c>
       <c r="K12" t="n">
-        <v>19.91124567498768</v>
+        <v>20.701580366233</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09581158458728</v>
+        <v>42.0774800385159</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90838975363711</v>
+        <v>99.90890604783647</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.87340805308546</v>
+        <v>76.92715611488069</v>
       </c>
       <c r="C13" t="n">
-        <v>36.1115361332422</v>
+        <v>35.18127869022278</v>
       </c>
       <c r="D13" t="n">
-        <v>1.545646034086655</v>
+        <v>1.507796756476467</v>
       </c>
       <c r="E13" t="n">
-        <v>9.952754202333919</v>
+        <v>9.666605894265352</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546653353264083</v>
+        <v>0.7546194006408861</v>
       </c>
       <c r="G13" t="n">
-        <v>23.89394725145782</v>
+        <v>23.28704778123833</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71460542501477</v>
+        <v>34.71249242948077</v>
       </c>
       <c r="I13" t="n">
-        <v>2.295131459075835</v>
+        <v>2.282222598773343</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716658345790051</v>
+        <v>4.716371254005538</v>
       </c>
       <c r="K13" t="n">
-        <v>22.12659194691453</v>
+        <v>23.07284388511931</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68544262353203</v>
+        <v>41.66987849418649</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92357070368875</v>
+        <v>99.92400106952859</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.28603825357811</v>
+        <v>83.59132412562192</v>
       </c>
       <c r="C14" t="n">
-        <v>40.07110823173708</v>
+        <v>39.36014693003048</v>
       </c>
       <c r="D14" t="n">
-        <v>1.547463717631293</v>
+        <v>1.509526736672392</v>
       </c>
       <c r="E14" t="n">
-        <v>12.1766152146793</v>
+        <v>11.99188544444743</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555528236202868</v>
+        <v>0.7554852180084869</v>
       </c>
       <c r="G14" t="n">
-        <v>25.63860019782402</v>
+        <v>25.1484096457553</v>
       </c>
       <c r="H14" t="n">
-        <v>36.47198349205573</v>
+        <v>36.58696335056401</v>
       </c>
       <c r="I14" t="n">
-        <v>2.973617660140683</v>
+        <v>2.877271117621278</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722205147626791</v>
+        <v>4.721782612553043</v>
       </c>
       <c r="K14" t="n">
-        <v>15.71396174642191</v>
+        <v>16.40867587437808</v>
       </c>
       <c r="L14" t="n">
-        <v>44.1159258623052</v>
+        <v>44.1353780740686</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90099584046419</v>
+        <v>99.90420087847716</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.727276547706</v>
+        <v>82.83820582674011</v>
       </c>
       <c r="C15" t="n">
-        <v>39.97247270068014</v>
+        <v>39.05180973456031</v>
       </c>
       <c r="D15" t="n">
-        <v>1.527003590420178</v>
+        <v>1.481541998049409</v>
       </c>
       <c r="E15" t="n">
-        <v>12.42902975482361</v>
+        <v>12.16957780388495</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562989444353397</v>
+        <v>0.7562148313927163</v>
       </c>
       <c r="G15" t="n">
-        <v>25.29961388390554</v>
+        <v>24.68218956920896</v>
       </c>
       <c r="H15" t="n">
-        <v>36.50800017440933</v>
+        <v>36.6222973816113</v>
       </c>
       <c r="I15" t="n">
-        <v>2.480461796991136</v>
+        <v>2.400041546388298</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726868402720872</v>
+        <v>4.726342696204477</v>
       </c>
       <c r="K15" t="n">
-        <v>16.27272345229399</v>
+        <v>17.1617941732599</v>
       </c>
       <c r="L15" t="n">
-        <v>43.67220335646643</v>
+        <v>43.70647189446811</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91739950944056</v>
+        <v>99.92007580228832</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.49143450857727</v>
+        <v>80.41029466675252</v>
       </c>
       <c r="C16" t="n">
-        <v>38.12061271737138</v>
+        <v>36.9949521462135</v>
       </c>
       <c r="D16" t="n">
-        <v>1.441250264867826</v>
+        <v>1.388857286555976</v>
       </c>
       <c r="E16" t="n">
-        <v>12.07584157270919</v>
+        <v>11.74186928571903</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569389428944234</v>
+        <v>0.7568423260278732</v>
       </c>
       <c r="G16" t="n">
-        <v>23.87884052138951</v>
+        <v>23.13808105101623</v>
       </c>
       <c r="H16" t="n">
-        <v>36.53889412716143</v>
+        <v>36.65268596191957</v>
       </c>
       <c r="I16" t="n">
-        <v>2.068800686464745</v>
+        <v>2.001694217839639</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730868393090145</v>
+        <v>4.730264537674207</v>
       </c>
       <c r="K16" t="n">
-        <v>18.50856549142271</v>
+        <v>19.58970533324747</v>
       </c>
       <c r="L16" t="n">
-        <v>43.30192007462282</v>
+        <v>43.34867469980602</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93109828341692</v>
+        <v>99.93333217926698</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>83.07704540822927</v>
+        <v>82.04624958867829</v>
       </c>
       <c r="C17" t="n">
-        <v>39.28633680670342</v>
+        <v>38.20078299644013</v>
       </c>
       <c r="D17" t="n">
-        <v>1.442440805077573</v>
+        <v>1.389971817143064</v>
       </c>
       <c r="E17" t="n">
-        <v>12.82458150816213</v>
+        <v>12.50393118219016</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575642099072426</v>
+        <v>0.7574496770711565</v>
       </c>
       <c r="G17" t="n">
-        <v>24.29420263746206</v>
+        <v>23.58008569515052</v>
       </c>
       <c r="H17" t="n">
-        <v>36.96471404035821</v>
+        <v>37.10553581001501</v>
       </c>
       <c r="I17" t="n">
-        <v>2.058765895341783</v>
+        <v>1.975214925413648</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734776311920265</v>
+        <v>4.734060481694728</v>
       </c>
       <c r="K17" t="n">
-        <v>16.92295459177073</v>
+        <v>17.95375041132171</v>
       </c>
       <c r="L17" t="n">
-        <v>43.72213971279416</v>
+        <v>43.77967888805978</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93143111126831</v>
+        <v>99.93421229582162</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.80158984923419</v>
+        <v>79.59460958667908</v>
       </c>
       <c r="C18" t="n">
-        <v>37.32927330930028</v>
+        <v>36.05413377586314</v>
       </c>
       <c r="D18" t="n">
-        <v>1.358285293190071</v>
+        <v>1.299932545595024</v>
       </c>
       <c r="E18" t="n">
-        <v>12.36250639569156</v>
+        <v>11.96847907695126</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581007615036794</v>
+        <v>0.7579721712567584</v>
       </c>
       <c r="G18" t="n">
-        <v>22.87681964908747</v>
+        <v>22.05262038049718</v>
       </c>
       <c r="H18" t="n">
-        <v>36.99089462818272</v>
+        <v>37.13113147306861</v>
       </c>
       <c r="I18" t="n">
-        <v>1.716853362180691</v>
+        <v>1.647147868955494</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738129759397995</v>
+        <v>4.73732607035474</v>
       </c>
       <c r="K18" t="n">
-        <v>19.19841015076582</v>
+        <v>20.40539041332093</v>
       </c>
       <c r="L18" t="n">
-        <v>43.41512859839663</v>
+        <v>43.48560872955444</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94281205846272</v>
+        <v>99.94513291873851</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.87002908762847</v>
+        <v>78.59216664082673</v>
       </c>
       <c r="C19" t="n">
-        <v>36.66260319372549</v>
+        <v>35.30533176580282</v>
       </c>
       <c r="D19" t="n">
-        <v>1.324502167591517</v>
+        <v>1.263775013724831</v>
       </c>
       <c r="E19" t="n">
-        <v>12.29362178784734</v>
+        <v>11.86448047600352</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585536936938784</v>
+        <v>0.7584136979804514</v>
       </c>
       <c r="G19" t="n">
-        <v>22.30782985336827</v>
+        <v>21.43922830339974</v>
       </c>
       <c r="H19" t="n">
-        <v>37.01299507679344</v>
+        <v>37.15276074581504</v>
       </c>
       <c r="I19" t="n">
-        <v>1.43156592274728</v>
+        <v>1.373422791525318</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740960585586738</v>
+        <v>4.740085612377822</v>
       </c>
       <c r="K19" t="n">
-        <v>20.12997091237153</v>
+        <v>21.40783335917327</v>
       </c>
       <c r="L19" t="n">
-        <v>43.15973552273129</v>
+        <v>43.24108076755293</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95230962882832</v>
+        <v>99.95424589252902</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.41145794683726</v>
+        <v>75.95667474625323</v>
       </c>
       <c r="C20" t="n">
-        <v>34.42476496209137</v>
+        <v>32.88115876202465</v>
       </c>
       <c r="D20" t="n">
-        <v>1.234494805980767</v>
+        <v>1.168009013685368</v>
       </c>
       <c r="E20" t="n">
-        <v>11.65713192758123</v>
+        <v>11.1562661170685</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589435576477114</v>
+        <v>0.7587948165949937</v>
       </c>
       <c r="G20" t="n">
-        <v>20.79188751858574</v>
+        <v>19.81461227898728</v>
       </c>
       <c r="H20" t="n">
-        <v>37.03201816339075</v>
+        <v>37.1714307787266</v>
       </c>
       <c r="I20" t="n">
-        <v>1.193584738352866</v>
+        <v>1.145094137471767</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743397235298195</v>
+        <v>4.742467603718711</v>
       </c>
       <c r="K20" t="n">
-        <v>22.58854205316274</v>
+        <v>24.04332525374679</v>
       </c>
       <c r="L20" t="n">
-        <v>42.94692726466958</v>
+        <v>43.03736535113063</v>
       </c>
       <c r="M20" t="n">
-        <v>99.9602342799237</v>
+        <v>99.96184936690207</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.76635171226626</v>
+        <v>81.74515738526283</v>
       </c>
       <c r="C21" t="n">
-        <v>37.68683200733912</v>
+        <v>36.48608671025218</v>
       </c>
       <c r="D21" t="n">
-        <v>1.235375662114279</v>
+        <v>1.16878710744036</v>
       </c>
       <c r="E21" t="n">
-        <v>13.43643616452091</v>
+        <v>13.09523622274072</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594850909814321</v>
+        <v>0.7593003037112701</v>
       </c>
       <c r="G21" t="n">
-        <v>22.28242599032854</v>
+        <v>21.48706904992741</v>
       </c>
       <c r="H21" t="n">
-        <v>38.53414454835782</v>
+        <v>38.85545015913543</v>
       </c>
       <c r="I21" t="n">
-        <v>1.771702437329318</v>
+        <v>1.633687644112185</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746781818633949</v>
+        <v>4.745626898195439</v>
       </c>
       <c r="K21" t="n">
-        <v>17.23364828773372</v>
+        <v>18.25484261473717</v>
       </c>
       <c r="L21" t="n">
-        <v>45.02050506606869</v>
+        <v>45.20465067323496</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94098536114154</v>
+        <v>99.94557999822432</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_84_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_84_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.61814364338967</v>
+        <v>45.59091323099246</v>
       </c>
       <c r="M2" t="n">
-        <v>99.60797179355185</v>
+        <v>98.63329993827301</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.01996011827684</v>
+        <v>87.96284203684378</v>
       </c>
       <c r="C3" t="n">
-        <v>45.91557340087468</v>
+        <v>45.87941263314262</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228721706626649</v>
+        <v>2.228602525279869</v>
       </c>
       <c r="E3" t="n">
-        <v>5.69849276108581</v>
+        <v>5.674756212843142</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429072355422166</v>
+        <v>0.7428675084266231</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96864292621975</v>
+        <v>33.95667994202486</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17373283494196</v>
+        <v>34.17190538762465</v>
       </c>
       <c r="I3" t="n">
-        <v>6.564292431721612</v>
+        <v>6.545108532978244</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643170222138854</v>
+        <v>4.642921927666394</v>
       </c>
       <c r="K3" t="n">
-        <v>11.98003988172314</v>
+        <v>12.03715796315622</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86876133942145</v>
+        <v>48.84848006809789</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7643746220193</v>
+        <v>106.7650506643967</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.11523581547327</v>
+        <v>87.01265630916879</v>
       </c>
       <c r="C4" t="n">
-        <v>42.64574760885442</v>
+        <v>42.56176331270205</v>
       </c>
       <c r="D4" t="n">
-        <v>2.185167139052318</v>
+        <v>2.18257560781099</v>
       </c>
       <c r="E4" t="n">
-        <v>6.500750130285947</v>
+        <v>6.468502746155032</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444654809949294</v>
+        <v>0.7444229427358743</v>
       </c>
       <c r="G4" t="n">
-        <v>33.30481417212299</v>
+        <v>33.25537888565437</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24541212576675</v>
+        <v>34.24345536585021</v>
       </c>
       <c r="I4" t="n">
-        <v>5.481717511032037</v>
+        <v>5.465677368863113</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652909256218308</v>
+        <v>4.652643392099214</v>
       </c>
       <c r="K4" t="n">
-        <v>12.88476418452671</v>
+        <v>12.9873436908312</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28714675018216</v>
+        <v>44.26908442610625</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81765854356328</v>
+        <v>99.8181914296395</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.01242687101117</v>
+        <v>85.87647664418445</v>
       </c>
       <c r="C5" t="n">
-        <v>42.39373763230405</v>
+        <v>42.27382237415844</v>
       </c>
       <c r="D5" t="n">
-        <v>2.131551301362659</v>
+        <v>2.127161695655085</v>
       </c>
       <c r="E5" t="n">
-        <v>7.103945890053355</v>
+        <v>7.064738762771221</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745785764015135</v>
+        <v>0.7457413679765521</v>
       </c>
       <c r="G5" t="n">
-        <v>32.48763846092717</v>
+        <v>32.41105045199738</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30614514469621</v>
+        <v>34.3041029269214</v>
       </c>
       <c r="I5" t="n">
-        <v>4.576199284862048</v>
+        <v>4.56279788900936</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661161025094593</v>
+        <v>4.660883549853451</v>
       </c>
       <c r="K5" t="n">
-        <v>13.98757312898885</v>
+        <v>14.12352335581556</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46641930784509</v>
+        <v>43.45082989866869</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84773006913797</v>
+        <v>99.84817562864268</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.67729348701731</v>
+        <v>84.57934472638757</v>
       </c>
       <c r="C6" t="n">
-        <v>41.7693712663731</v>
+        <v>41.68528228963245</v>
       </c>
       <c r="D6" t="n">
-        <v>2.06644413895934</v>
+        <v>2.06393210978321</v>
       </c>
       <c r="E6" t="n">
-        <v>7.523498235123562</v>
+        <v>7.489413387884492</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469070128297082</v>
+        <v>0.7468605582829843</v>
       </c>
       <c r="G6" t="n">
-        <v>31.49531988430003</v>
+        <v>31.44763648025362</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35772259016657</v>
+        <v>34.35558568101727</v>
       </c>
       <c r="I6" t="n">
-        <v>3.819232795452406</v>
+        <v>3.808038019897337</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668168830185675</v>
+        <v>4.667878489268652</v>
       </c>
       <c r="K6" t="n">
-        <v>15.32270651298269</v>
+        <v>15.42065527361242</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78080557384251</v>
+        <v>42.76731805094931</v>
       </c>
       <c r="M6" t="n">
-        <v>99.8728833531983</v>
+        <v>99.87325561419419</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.17103510118037</v>
+        <v>83.11226890611442</v>
       </c>
       <c r="C7" t="n">
-        <v>40.85635988474411</v>
+        <v>40.80966088536132</v>
       </c>
       <c r="D7" t="n">
-        <v>1.993227126199026</v>
+        <v>1.992617612863581</v>
       </c>
       <c r="E7" t="n">
-        <v>7.788056629626013</v>
+        <v>7.760201842847666</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478609557382109</v>
+        <v>0.7478123156559549</v>
       </c>
       <c r="G7" t="n">
-        <v>30.37939654798363</v>
+        <v>30.36103466604171</v>
       </c>
       <c r="H7" t="n">
-        <v>34.4016039639577</v>
+        <v>34.39936652017392</v>
       </c>
       <c r="I7" t="n">
-        <v>3.186758904311973</v>
+        <v>3.177408975681862</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674130973363818</v>
+        <v>4.673826972849719</v>
       </c>
       <c r="K7" t="n">
-        <v>16.82896489881962</v>
+        <v>16.88773109388559</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20858541656259</v>
+        <v>42.19682918686704</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89391020012631</v>
+        <v>99.89422116611395</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.95245000526972</v>
+        <v>88.02148806886295</v>
       </c>
       <c r="C8" t="n">
-        <v>43.06107440230609</v>
+        <v>43.0851492977155</v>
       </c>
       <c r="D8" t="n">
-        <v>1.997487738837761</v>
+        <v>1.996908414149221</v>
       </c>
       <c r="E8" t="n">
-        <v>9.556130667161185</v>
+        <v>9.578327778926971</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494595421703107</v>
+        <v>0.7494226166112008</v>
       </c>
       <c r="G8" t="n">
-        <v>30.85004143758328</v>
+        <v>30.85326785424488</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4751389398343</v>
+        <v>34.47344036411523</v>
       </c>
       <c r="I8" t="n">
-        <v>5.640069541118432</v>
+        <v>5.686229686995447</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684122138564442</v>
+        <v>4.683891353820006</v>
       </c>
       <c r="K8" t="n">
-        <v>12.04754999473029</v>
+        <v>11.97851193113704</v>
       </c>
       <c r="L8" t="n">
-        <v>44.70377429116871</v>
+        <v>44.7472050524983</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81239868820508</v>
+        <v>99.81086628135084</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.01814909714911</v>
+        <v>86.0676382829682</v>
       </c>
       <c r="C9" t="n">
-        <v>42.00216146945395</v>
+        <v>42.01383100123133</v>
       </c>
       <c r="D9" t="n">
-        <v>1.909848094582238</v>
+        <v>1.908452353913707</v>
       </c>
       <c r="E9" t="n">
-        <v>9.921628389259743</v>
+        <v>9.945247490541808</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508270561628548</v>
+        <v>0.7508004812478762</v>
       </c>
       <c r="G9" t="n">
-        <v>29.49649788170089</v>
+        <v>29.48657597171292</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53804458349133</v>
+        <v>34.5368221374023</v>
       </c>
       <c r="I9" t="n">
-        <v>4.708633990934207</v>
+        <v>4.747236840350355</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692669101017843</v>
+        <v>4.692503007799227</v>
       </c>
       <c r="K9" t="n">
-        <v>13.98185090285089</v>
+        <v>13.9323617170318</v>
       </c>
       <c r="L9" t="n">
-        <v>43.85931902933077</v>
+        <v>43.89585645709811</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84333140163561</v>
+        <v>99.84204917536124</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.83767545157569</v>
+        <v>83.93354896508495</v>
       </c>
       <c r="C10" t="n">
-        <v>40.5523047193176</v>
+        <v>40.61632542958171</v>
       </c>
       <c r="D10" t="n">
-        <v>1.811910827099061</v>
+        <v>1.812781283366554</v>
       </c>
       <c r="E10" t="n">
-        <v>10.06784475797791</v>
+        <v>10.1070663531508</v>
       </c>
       <c r="F10" t="n">
-        <v>0.752000253832344</v>
+        <v>0.7519819172717596</v>
       </c>
       <c r="G10" t="n">
-        <v>27.98391349813032</v>
+        <v>28.00840844806549</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59201167628784</v>
+        <v>34.59116819450094</v>
       </c>
       <c r="I10" t="n">
-        <v>3.92999285179607</v>
+        <v>3.962255785780913</v>
       </c>
       <c r="J10" t="n">
-        <v>4.70000158645215</v>
+        <v>4.699886982948498</v>
       </c>
       <c r="K10" t="n">
-        <v>16.16232454842432</v>
+        <v>16.06645103491506</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15457534362101</v>
+        <v>43.18535584549349</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86920461136293</v>
+        <v>99.86813230999026</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.58145663322665</v>
+        <v>81.71725715756052</v>
       </c>
       <c r="C11" t="n">
-        <v>38.90528285921785</v>
+        <v>39.01425949791088</v>
       </c>
       <c r="D11" t="n">
-        <v>1.711650029572799</v>
+        <v>1.714468669995701</v>
       </c>
       <c r="E11" t="n">
-        <v>10.05731143852874</v>
+        <v>10.10998507162499</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530078750930068</v>
+        <v>0.7529961064144649</v>
       </c>
       <c r="G11" t="n">
-        <v>26.43544353853495</v>
+        <v>26.4894277215137</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63836225427833</v>
+        <v>34.63782089506538</v>
       </c>
       <c r="I11" t="n">
-        <v>3.27938227788754</v>
+        <v>3.306333027855886</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706299219331292</v>
+        <v>4.706225665090406</v>
       </c>
       <c r="K11" t="n">
-        <v>18.41854336677335</v>
+        <v>18.28274284243946</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56700730590338</v>
+        <v>42.59293499893353</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89083353189457</v>
+        <v>99.88993733928388</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.29841963376698</v>
+        <v>79.40486562847956</v>
       </c>
       <c r="C12" t="n">
-        <v>37.12984564308756</v>
+        <v>37.2136989610034</v>
       </c>
       <c r="D12" t="n">
-        <v>1.611215314676974</v>
+        <v>1.612859320362928</v>
       </c>
       <c r="E12" t="n">
-        <v>9.923170829498321</v>
+        <v>9.970553441709376</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538738866994108</v>
+        <v>0.7538680578996203</v>
       </c>
       <c r="G12" t="n">
-        <v>24.88428752587734</v>
+        <v>24.91951071455311</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67819878817291</v>
+        <v>34.67793066338253</v>
       </c>
       <c r="I12" t="n">
-        <v>2.735961496970722</v>
+        <v>2.758468068699351</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711711791871317</v>
+        <v>4.711675361872627</v>
       </c>
       <c r="K12" t="n">
-        <v>20.701580366233</v>
+        <v>20.59513437152045</v>
       </c>
       <c r="L12" t="n">
-        <v>42.0774800385159</v>
+        <v>42.09932408336903</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90890604783647</v>
+        <v>99.90815741589287</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.92715611488069</v>
+        <v>76.98612813579554</v>
       </c>
       <c r="C13" t="n">
-        <v>35.18127869022278</v>
+        <v>35.22117460693815</v>
       </c>
       <c r="D13" t="n">
-        <v>1.507796756476467</v>
+        <v>1.50748928597688</v>
       </c>
       <c r="E13" t="n">
-        <v>9.666605894265352</v>
+        <v>9.702667487448167</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546194006408861</v>
+        <v>0.7546191285508252</v>
       </c>
       <c r="G13" t="n">
-        <v>23.28704778123833</v>
+        <v>23.29148918302543</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71249242948077</v>
+        <v>34.71247991333796</v>
       </c>
       <c r="I13" t="n">
-        <v>2.282222598773343</v>
+        <v>2.301013584013611</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716371254005538</v>
+        <v>4.716369553442657</v>
       </c>
       <c r="K13" t="n">
-        <v>23.07284388511931</v>
+        <v>23.01387186420447</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66987849418649</v>
+        <v>41.68832941583796</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92400106952859</v>
+        <v>99.92337588698058</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.59132412562192</v>
+        <v>83.58129066408452</v>
       </c>
       <c r="C14" t="n">
-        <v>39.36014693003048</v>
+        <v>39.37157683198504</v>
       </c>
       <c r="D14" t="n">
-        <v>1.509526736672392</v>
+        <v>1.509214638997476</v>
       </c>
       <c r="E14" t="n">
-        <v>11.99188544444743</v>
+        <v>12.0129346356985</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554852180084869</v>
+        <v>0.7554828059281412</v>
       </c>
       <c r="G14" t="n">
-        <v>25.1484096457553</v>
+        <v>25.13900634459717</v>
       </c>
       <c r="H14" t="n">
-        <v>36.58696335056401</v>
+        <v>36.57306863769826</v>
       </c>
       <c r="I14" t="n">
-        <v>2.877271117621278</v>
+        <v>2.869816064114103</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721782612553043</v>
+        <v>4.721767537050882</v>
       </c>
       <c r="K14" t="n">
-        <v>16.40867587437808</v>
+        <v>16.41870933591549</v>
       </c>
       <c r="L14" t="n">
-        <v>44.1353780740686</v>
+        <v>44.11416265694766</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90420087847716</v>
+        <v>99.90444882484817</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.83820582674011</v>
+        <v>82.89426362065259</v>
       </c>
       <c r="C15" t="n">
-        <v>39.05180973456031</v>
+        <v>39.12819694624966</v>
       </c>
       <c r="D15" t="n">
-        <v>1.481541998049409</v>
+        <v>1.483822130735494</v>
       </c>
       <c r="E15" t="n">
-        <v>12.16957780388495</v>
+        <v>12.20978647574529</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562148313927163</v>
+        <v>0.756210032130153</v>
       </c>
       <c r="G15" t="n">
-        <v>24.68218956920896</v>
+        <v>24.71604302989779</v>
       </c>
       <c r="H15" t="n">
-        <v>36.6222973816113</v>
+        <v>36.60827379867957</v>
       </c>
       <c r="I15" t="n">
-        <v>2.400041546388298</v>
+        <v>2.393815452650834</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726342696204477</v>
+        <v>4.726312700813455</v>
       </c>
       <c r="K15" t="n">
-        <v>17.1617941732599</v>
+        <v>17.10573637934741</v>
       </c>
       <c r="L15" t="n">
-        <v>43.70647189446811</v>
+        <v>43.68634956151089</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92007580228832</v>
+        <v>99.92028288710796</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.41029466675252</v>
+        <v>80.60497523650469</v>
       </c>
       <c r="C16" t="n">
-        <v>36.9949521462135</v>
+        <v>37.20904765278453</v>
       </c>
       <c r="D16" t="n">
-        <v>1.388857286555976</v>
+        <v>1.396535574526681</v>
       </c>
       <c r="E16" t="n">
-        <v>11.74186928571903</v>
+        <v>11.82428873568663</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568423260278732</v>
+        <v>0.7568343807687058</v>
       </c>
       <c r="G16" t="n">
-        <v>23.13808105101623</v>
+        <v>23.26210981613768</v>
       </c>
       <c r="H16" t="n">
-        <v>36.65268596191957</v>
+        <v>36.63849863693196</v>
       </c>
       <c r="I16" t="n">
-        <v>2.001694217839639</v>
+        <v>1.996493212648597</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730264537674207</v>
+        <v>4.73021487980441</v>
       </c>
       <c r="K16" t="n">
-        <v>19.58970533324747</v>
+        <v>19.39502476349533</v>
       </c>
       <c r="L16" t="n">
-        <v>43.34867469980602</v>
+        <v>43.32943271003539</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93333217926698</v>
+        <v>99.93350512631525</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.04624958867829</v>
+        <v>82.33810354619678</v>
       </c>
       <c r="C17" t="n">
-        <v>38.20078299644013</v>
+        <v>38.47360383553129</v>
       </c>
       <c r="D17" t="n">
-        <v>1.389971817143064</v>
+        <v>1.39765462722564</v>
       </c>
       <c r="E17" t="n">
-        <v>12.50393118219016</v>
+        <v>12.61612071110454</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574496770711565</v>
+        <v>0.7574408368962209</v>
       </c>
       <c r="G17" t="n">
-        <v>23.58008569515052</v>
+        <v>23.73321679992451</v>
       </c>
       <c r="H17" t="n">
-        <v>37.10553581001501</v>
+        <v>37.12032420482454</v>
       </c>
       <c r="I17" t="n">
-        <v>1.975214925413648</v>
+        <v>1.979341135619943</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734060481694728</v>
+        <v>4.734005230601379</v>
       </c>
       <c r="K17" t="n">
-        <v>17.95375041132171</v>
+        <v>17.66189645380322</v>
       </c>
       <c r="L17" t="n">
-        <v>43.77967888805978</v>
+        <v>43.79857449909625</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93421229582162</v>
+        <v>99.93407478843076</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.59460958667908</v>
+        <v>80.10385193834891</v>
       </c>
       <c r="C18" t="n">
-        <v>36.05413377586314</v>
+        <v>36.54508985836139</v>
       </c>
       <c r="D18" t="n">
-        <v>1.299932545595024</v>
+        <v>1.3158303452505</v>
       </c>
       <c r="E18" t="n">
-        <v>11.96847907695126</v>
+        <v>12.15261994757197</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579721712567584</v>
+        <v>0.7579610863810978</v>
       </c>
       <c r="G18" t="n">
-        <v>22.05262038049718</v>
+        <v>22.34377953424683</v>
       </c>
       <c r="H18" t="n">
-        <v>37.13113147306861</v>
+        <v>37.14582036057072</v>
       </c>
       <c r="I18" t="n">
-        <v>1.647147868955494</v>
+        <v>1.65058387444594</v>
       </c>
       <c r="J18" t="n">
-        <v>4.73732607035474</v>
+        <v>4.73725678988186</v>
       </c>
       <c r="K18" t="n">
-        <v>20.40539041332093</v>
+        <v>19.89614806165107</v>
       </c>
       <c r="L18" t="n">
-        <v>43.48560872955444</v>
+        <v>43.50378038177587</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94513291873851</v>
+        <v>99.94501830178834</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.59216664082673</v>
+        <v>79.23286501009522</v>
       </c>
       <c r="C19" t="n">
-        <v>35.30533176580282</v>
+        <v>35.9280290486082</v>
       </c>
       <c r="D19" t="n">
-        <v>1.263775013724831</v>
+        <v>1.284553636105377</v>
       </c>
       <c r="E19" t="n">
-        <v>11.86448047600352</v>
+        <v>12.09320626262945</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584136979804514</v>
+        <v>0.7584000790261839</v>
       </c>
       <c r="G19" t="n">
-        <v>21.43922830339974</v>
+        <v>21.81267771233046</v>
       </c>
       <c r="H19" t="n">
-        <v>37.15276074581504</v>
+        <v>37.16733431719327</v>
       </c>
       <c r="I19" t="n">
-        <v>1.373422791525318</v>
+        <v>1.376692508896825</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740085612377822</v>
+        <v>4.740000493913648</v>
       </c>
       <c r="K19" t="n">
-        <v>21.40783335917327</v>
+        <v>20.76713498990476</v>
       </c>
       <c r="L19" t="n">
-        <v>43.24108076755293</v>
+        <v>43.25897277403431</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95424589252902</v>
+        <v>99.95413681254728</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.95667474625323</v>
+        <v>76.68457194661292</v>
       </c>
       <c r="C20" t="n">
-        <v>32.88115876202465</v>
+        <v>33.59175191951149</v>
       </c>
       <c r="D20" t="n">
-        <v>1.168009013685368</v>
+        <v>1.192128001542602</v>
       </c>
       <c r="E20" t="n">
-        <v>11.1562661170685</v>
+        <v>11.41438393191026</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587948165949937</v>
+        <v>0.7587784705946365</v>
       </c>
       <c r="G20" t="n">
-        <v>19.81461227898728</v>
+        <v>20.243221581882</v>
       </c>
       <c r="H20" t="n">
-        <v>37.1714307787266</v>
+        <v>37.18587836316113</v>
       </c>
       <c r="I20" t="n">
-        <v>1.145094137471767</v>
+        <v>1.147816156305808</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742467603718711</v>
+        <v>4.742365441216477</v>
       </c>
       <c r="K20" t="n">
-        <v>24.04332525374679</v>
+        <v>23.31542805338708</v>
       </c>
       <c r="L20" t="n">
-        <v>43.03736535113063</v>
+        <v>43.05457856852095</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96184936690207</v>
+        <v>99.96175854141953</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.74515738526283</v>
+        <v>82.18822994166646</v>
       </c>
       <c r="C21" t="n">
-        <v>36.48608671025218</v>
+        <v>37.04094575196171</v>
       </c>
       <c r="D21" t="n">
-        <v>1.16878710744036</v>
+        <v>1.192893342765301</v>
       </c>
       <c r="E21" t="n">
-        <v>13.09523622274072</v>
+        <v>13.27094186123476</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593003037112701</v>
+        <v>0.7592656032193976</v>
       </c>
       <c r="G21" t="n">
-        <v>21.48706904992741</v>
+        <v>21.84162507797884</v>
       </c>
       <c r="H21" t="n">
-        <v>38.85545015913543</v>
+        <v>38.7951589745006</v>
       </c>
       <c r="I21" t="n">
-        <v>1.633687644112185</v>
+        <v>1.582935061846331</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745626898195439</v>
+        <v>4.745410020121234</v>
       </c>
       <c r="K21" t="n">
-        <v>18.25484261473717</v>
+        <v>17.81177005833354</v>
       </c>
       <c r="L21" t="n">
-        <v>45.20465067323496</v>
+        <v>45.09455354050084</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94557999822432</v>
+        <v>99.94726935079609</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_84_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_84_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.59091323099246</v>
+        <v>43.99485550492142</v>
       </c>
       <c r="M2" t="n">
-        <v>98.63329993827301</v>
+        <v>92.18661173669838</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.96284203684378</v>
+        <v>81.51477615520977</v>
       </c>
       <c r="C3" t="n">
-        <v>45.87941263314262</v>
+        <v>43.27033171076533</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228602525279869</v>
+        <v>2.182105765857688</v>
       </c>
       <c r="E3" t="n">
-        <v>5.674756212843142</v>
+        <v>4.156201791774154</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428675084266231</v>
+        <v>0.737659698742558</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95667994202486</v>
+        <v>32.82250756144273</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17190538762465</v>
+        <v>33.93234614215766</v>
       </c>
       <c r="I3" t="n">
-        <v>6.545108532978244</v>
+        <v>3.073582078093992</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642921927666394</v>
+        <v>4.610373117140988</v>
       </c>
       <c r="K3" t="n">
-        <v>12.03715796315622</v>
+        <v>18.48522384479022</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84848006809789</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7650506643967</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.01265630916879</v>
+        <v>88.62363563451619</v>
       </c>
       <c r="C4" t="n">
-        <v>42.56176331270205</v>
+        <v>42.88612935319755</v>
       </c>
       <c r="D4" t="n">
-        <v>2.18257560781099</v>
+        <v>2.18783532645526</v>
       </c>
       <c r="E4" t="n">
-        <v>6.468502746155032</v>
+        <v>6.551946397845095</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444229427358743</v>
+        <v>0.7395965736688156</v>
       </c>
       <c r="G4" t="n">
-        <v>33.25537888565437</v>
+        <v>33.51935727293289</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24345536585021</v>
+        <v>34.02144238876551</v>
       </c>
       <c r="I4" t="n">
-        <v>5.465677368863113</v>
+        <v>6.980979089418533</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652643392099214</v>
+        <v>4.622478585430097</v>
       </c>
       <c r="K4" t="n">
-        <v>12.9873436908312</v>
+        <v>11.37636436548379</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26908442610625</v>
+        <v>45.50541637738252</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8181914296395</v>
+        <v>99.76791009606387</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.87647664418445</v>
+        <v>87.51799941806377</v>
       </c>
       <c r="C5" t="n">
-        <v>42.27382237415844</v>
+        <v>42.86267978353553</v>
       </c>
       <c r="D5" t="n">
-        <v>2.127161695655085</v>
+        <v>2.135325755467167</v>
       </c>
       <c r="E5" t="n">
-        <v>7.064738762771221</v>
+        <v>7.366428649198141</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457413679765521</v>
+        <v>0.7412389576157961</v>
       </c>
       <c r="G5" t="n">
-        <v>32.41105045199738</v>
+        <v>32.71486936247849</v>
       </c>
       <c r="H5" t="n">
-        <v>34.3041029269214</v>
+        <v>34.09699205032661</v>
       </c>
       <c r="I5" t="n">
-        <v>4.56279788900936</v>
+        <v>5.83040115787884</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660883549853451</v>
+        <v>4.632743485098725</v>
       </c>
       <c r="K5" t="n">
-        <v>14.12352335581556</v>
+        <v>12.48200058193623</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45082989866869</v>
+        <v>44.46140354871105</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84817562864268</v>
+        <v>99.80608391418281</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.57934472638757</v>
+        <v>86.07744938149087</v>
       </c>
       <c r="C6" t="n">
-        <v>41.68528228963245</v>
+        <v>42.32709062678095</v>
       </c>
       <c r="D6" t="n">
-        <v>2.06393210978321</v>
+        <v>2.066350288934657</v>
       </c>
       <c r="E6" t="n">
-        <v>7.489413387884492</v>
+        <v>7.939782086801047</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468605582829843</v>
+        <v>0.7426362351698185</v>
       </c>
       <c r="G6" t="n">
-        <v>31.44763648025362</v>
+        <v>31.65811098683037</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35558568101727</v>
+        <v>34.16126681781164</v>
       </c>
       <c r="I6" t="n">
-        <v>3.808038019897337</v>
+        <v>4.867826496131964</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667878489268652</v>
+        <v>4.641476469811366</v>
       </c>
       <c r="K6" t="n">
-        <v>15.42065527361242</v>
+        <v>13.92255061850915</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76731805094931</v>
+        <v>43.58840316699103</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87325561419419</v>
+        <v>99.83804441228114</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.11226890611442</v>
+        <v>84.32917302569875</v>
       </c>
       <c r="C7" t="n">
-        <v>40.80966088536132</v>
+        <v>41.33469025529546</v>
       </c>
       <c r="D7" t="n">
-        <v>1.992617612863581</v>
+        <v>1.982823366882438</v>
       </c>
       <c r="E7" t="n">
-        <v>7.760201842847666</v>
+        <v>8.296009540534321</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478123156559549</v>
+        <v>0.743828925810203</v>
       </c>
       <c r="G7" t="n">
-        <v>30.36103466604171</v>
+        <v>30.37841287229588</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39936652017392</v>
+        <v>34.21613058726932</v>
       </c>
       <c r="I7" t="n">
-        <v>3.177408975681862</v>
+        <v>4.063036946592823</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673826972849719</v>
+        <v>4.648930786313769</v>
       </c>
       <c r="K7" t="n">
-        <v>16.88773109388559</v>
+        <v>15.67082697430124</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19682918686704</v>
+        <v>42.85926536773297</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89422116611395</v>
+        <v>99.86478259732968</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.02148806886295</v>
+        <v>82.33682812592649</v>
       </c>
       <c r="C8" t="n">
-        <v>43.0851492977155</v>
+        <v>39.97304049277737</v>
       </c>
       <c r="D8" t="n">
-        <v>1.996908414149221</v>
+        <v>1.888246490549585</v>
       </c>
       <c r="E8" t="n">
-        <v>9.578327778926971</v>
+        <v>8.465391047484655</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494226166112008</v>
+        <v>0.7448499191595458</v>
       </c>
       <c r="G8" t="n">
-        <v>30.85326785424488</v>
+        <v>28.92942077073072</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47344036411523</v>
+        <v>34.26309628133909</v>
       </c>
       <c r="I8" t="n">
-        <v>5.686229686995447</v>
+        <v>3.390511621915739</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683891353820006</v>
+        <v>4.655311994747161</v>
       </c>
       <c r="K8" t="n">
-        <v>11.97851193113704</v>
+        <v>17.6631718740735</v>
       </c>
       <c r="L8" t="n">
-        <v>44.7472050524983</v>
+        <v>42.25092549574377</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81086628135084</v>
+        <v>99.88713786259464</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.0676382829682</v>
+        <v>80.08336409450484</v>
       </c>
       <c r="C9" t="n">
-        <v>42.01383100123133</v>
+        <v>38.24534858843556</v>
       </c>
       <c r="D9" t="n">
-        <v>1.908452353913707</v>
+        <v>1.782023367133094</v>
       </c>
       <c r="E9" t="n">
-        <v>9.945247490541808</v>
+        <v>8.46063013839413</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508004812478762</v>
+        <v>0.7457269204843758</v>
       </c>
       <c r="G9" t="n">
-        <v>29.48657597171292</v>
+        <v>27.30199900758871</v>
       </c>
       <c r="H9" t="n">
-        <v>34.5368221374023</v>
+        <v>34.30343834228128</v>
       </c>
       <c r="I9" t="n">
-        <v>4.747236840350355</v>
+        <v>2.828753065595903</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692503007799227</v>
+        <v>4.660793253027349</v>
       </c>
       <c r="K9" t="n">
-        <v>13.9323617170318</v>
+        <v>19.91663590549518</v>
       </c>
       <c r="L9" t="n">
-        <v>43.89585645709811</v>
+        <v>41.74383462768269</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84204917536124</v>
+        <v>99.90581912161343</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.93354896508495</v>
+        <v>85.22361712861084</v>
       </c>
       <c r="C10" t="n">
-        <v>40.61632542958171</v>
+        <v>41.78989026071955</v>
       </c>
       <c r="D10" t="n">
-        <v>1.812781283366554</v>
+        <v>1.784021031454142</v>
       </c>
       <c r="E10" t="n">
-        <v>10.1070663531508</v>
+        <v>10.46067260164603</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519819172717596</v>
+        <v>0.7465628871107244</v>
       </c>
       <c r="G10" t="n">
-        <v>28.00840844806549</v>
+        <v>28.8454805856702</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59116819450094</v>
+        <v>35.85476859721676</v>
       </c>
       <c r="I10" t="n">
-        <v>3.962255785780913</v>
+        <v>2.86609338107096</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699886982948498</v>
+        <v>4.666018044442027</v>
       </c>
       <c r="K10" t="n">
-        <v>16.06645103491506</v>
+        <v>14.77638287138917</v>
       </c>
       <c r="L10" t="n">
-        <v>43.18535584549349</v>
+        <v>43.33829739915365</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86813230999026</v>
+        <v>99.90457053126235</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.71725715756052</v>
+        <v>84.59291295097155</v>
       </c>
       <c r="C11" t="n">
-        <v>39.01425949791088</v>
+        <v>41.48948813578136</v>
       </c>
       <c r="D11" t="n">
-        <v>1.714468669995701</v>
+        <v>1.748857038587483</v>
       </c>
       <c r="E11" t="n">
-        <v>10.10998507162499</v>
+        <v>10.71028404894374</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529961064144649</v>
+        <v>0.7472856642905804</v>
       </c>
       <c r="G11" t="n">
-        <v>26.4894277215137</v>
+        <v>28.32322900512876</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63782089506538</v>
+        <v>35.9357890362058</v>
       </c>
       <c r="I11" t="n">
-        <v>3.306333027855886</v>
+        <v>2.456932755999069</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706225665090406</v>
+        <v>4.670535401816127</v>
       </c>
       <c r="K11" t="n">
-        <v>18.28274284243946</v>
+        <v>15.40708704902845</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59293499893353</v>
+        <v>43.02160626844134</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88993733928388</v>
+        <v>99.91818145325114</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.40486562847956</v>
+        <v>82.18976146808509</v>
       </c>
       <c r="C12" t="n">
-        <v>37.2136989610034</v>
+        <v>39.46774493461952</v>
       </c>
       <c r="D12" t="n">
-        <v>1.612859320362928</v>
+        <v>1.64717124550441</v>
       </c>
       <c r="E12" t="n">
-        <v>9.970553441709376</v>
+        <v>10.42906801860639</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538680578996203</v>
+        <v>0.7479067055825568</v>
       </c>
       <c r="G12" t="n">
-        <v>24.91951071455311</v>
+        <v>26.67639913824255</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67793066338253</v>
+        <v>35.96565393248</v>
       </c>
       <c r="I12" t="n">
-        <v>2.758468068699351</v>
+        <v>2.049145517778198</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711675361872627</v>
+        <v>4.674416909890979</v>
       </c>
       <c r="K12" t="n">
-        <v>20.59513437152045</v>
+        <v>17.81023853191492</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09932408336903</v>
+        <v>42.65376840135448</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90815741589287</v>
+        <v>99.93175186788891</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.98612813579554</v>
+        <v>83.20042164222197</v>
       </c>
       <c r="C13" t="n">
-        <v>35.22117460693815</v>
+        <v>40.34398726151401</v>
       </c>
       <c r="D13" t="n">
-        <v>1.50748928597688</v>
+        <v>1.648418844804826</v>
       </c>
       <c r="E13" t="n">
-        <v>9.702667487448167</v>
+        <v>11.01655170642785</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546191285508252</v>
+        <v>0.7484731845598994</v>
       </c>
       <c r="G13" t="n">
-        <v>23.29148918302543</v>
+        <v>26.96110084052452</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71247991333796</v>
+        <v>36.2573914956746</v>
       </c>
       <c r="I13" t="n">
-        <v>2.301013584013611</v>
+        <v>1.890528166730891</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716369553442657</v>
+        <v>4.677957403499371</v>
       </c>
       <c r="K13" t="n">
-        <v>23.01387186420447</v>
+        <v>16.79957835777804</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68832941583796</v>
+        <v>42.79346446977645</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92337588698058</v>
+        <v>99.93703008906849</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.58129066408452</v>
+        <v>80.78834607270387</v>
       </c>
       <c r="C14" t="n">
-        <v>39.37157683198504</v>
+        <v>38.22504236328942</v>
       </c>
       <c r="D14" t="n">
-        <v>1.509214638997476</v>
+        <v>1.549085015355886</v>
       </c>
       <c r="E14" t="n">
-        <v>12.0129346356985</v>
+        <v>10.61543771387818</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554828059281412</v>
+        <v>0.7489600294041319</v>
       </c>
       <c r="G14" t="n">
-        <v>25.13900634459717</v>
+        <v>25.33642310701715</v>
       </c>
       <c r="H14" t="n">
-        <v>36.57306863769826</v>
+        <v>36.28097513832088</v>
       </c>
       <c r="I14" t="n">
-        <v>2.869816064114103</v>
+        <v>1.576464884951836</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721767537050882</v>
+        <v>4.681000183775824</v>
       </c>
       <c r="K14" t="n">
-        <v>16.41870933591549</v>
+        <v>19.21165392729611</v>
       </c>
       <c r="L14" t="n">
-        <v>44.11416265694766</v>
+        <v>42.51078903811639</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90444882484817</v>
+        <v>99.94748532870192</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.89426362065259</v>
+        <v>79.61104404324816</v>
       </c>
       <c r="C15" t="n">
-        <v>39.12819694624966</v>
+        <v>37.25624519105965</v>
       </c>
       <c r="D15" t="n">
-        <v>1.483822130735494</v>
+        <v>1.499605539707962</v>
       </c>
       <c r="E15" t="n">
-        <v>12.20978647574529</v>
+        <v>10.50114479428017</v>
       </c>
       <c r="F15" t="n">
-        <v>0.756210032130153</v>
+        <v>0.7493829558989658</v>
       </c>
       <c r="G15" t="n">
-        <v>24.71604302989779</v>
+        <v>24.5271499440196</v>
       </c>
       <c r="H15" t="n">
-        <v>36.60827379867957</v>
+        <v>36.30146246079737</v>
       </c>
       <c r="I15" t="n">
-        <v>2.393815452650834</v>
+        <v>1.348654874175548</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726312700813455</v>
+        <v>4.683643474368536</v>
       </c>
       <c r="K15" t="n">
-        <v>17.10573637934741</v>
+        <v>20.38895595675184</v>
       </c>
       <c r="L15" t="n">
-        <v>43.68634956151089</v>
+        <v>42.30986906089522</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92028288710796</v>
+        <v>99.95507020870672</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.60497523650469</v>
+        <v>76.85497389563905</v>
       </c>
       <c r="C16" t="n">
-        <v>37.20904765278453</v>
+        <v>34.70852626326641</v>
       </c>
       <c r="D16" t="n">
-        <v>1.396535574526681</v>
+        <v>1.387134809706039</v>
       </c>
       <c r="E16" t="n">
-        <v>11.82428873568663</v>
+        <v>9.900961258744136</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568343807687058</v>
+        <v>0.7497484176275037</v>
       </c>
       <c r="G16" t="n">
-        <v>23.26210981613768</v>
+        <v>22.68760855394996</v>
       </c>
       <c r="H16" t="n">
-        <v>36.63849863693196</v>
+        <v>36.31916608631347</v>
       </c>
       <c r="I16" t="n">
-        <v>1.996493212648597</v>
+        <v>1.124427159126039</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73021487980441</v>
+        <v>4.685927610171897</v>
       </c>
       <c r="K16" t="n">
-        <v>19.39502476349533</v>
+        <v>23.14502610436096</v>
       </c>
       <c r="L16" t="n">
-        <v>43.32943271003539</v>
+        <v>42.10898499697887</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93350512631525</v>
+        <v>99.96253736460623</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.33810354619678</v>
+        <v>82.33715125092365</v>
       </c>
       <c r="C17" t="n">
-        <v>38.47360383553129</v>
+        <v>38.35665883160919</v>
       </c>
       <c r="D17" t="n">
-        <v>1.39765462722564</v>
+        <v>1.387820730889432</v>
       </c>
       <c r="E17" t="n">
-        <v>12.61612071110454</v>
+        <v>11.82414463558415</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574408368962209</v>
+        <v>0.7501191590423019</v>
       </c>
       <c r="G17" t="n">
-        <v>23.73321679992451</v>
+        <v>24.41354120435921</v>
       </c>
       <c r="H17" t="n">
-        <v>37.12032420482454</v>
+        <v>38.0518393750577</v>
       </c>
       <c r="I17" t="n">
-        <v>1.979341135619943</v>
+        <v>1.22144140197648</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734005230601379</v>
+        <v>4.688244744014386</v>
       </c>
       <c r="K17" t="n">
-        <v>17.66189645380322</v>
+        <v>17.66284874907634</v>
       </c>
       <c r="L17" t="n">
-        <v>43.79857449909625</v>
+        <v>43.93979782889206</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93407478843076</v>
+        <v>99.9593054095776</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.10385193834891</v>
+        <v>83.9528330827567</v>
       </c>
       <c r="C18" t="n">
-        <v>36.54508985836139</v>
+        <v>39.05476279366525</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3158303452505</v>
+        <v>1.388972446457424</v>
       </c>
       <c r="E18" t="n">
-        <v>12.15261994757197</v>
+        <v>12.40320799798191</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579610863810978</v>
+        <v>0.7507416630113589</v>
       </c>
       <c r="G18" t="n">
-        <v>22.34377953424683</v>
+        <v>24.54425119667355</v>
       </c>
       <c r="H18" t="n">
-        <v>37.14582036057072</v>
+        <v>38.08341758600639</v>
       </c>
       <c r="I18" t="n">
-        <v>1.65058387444594</v>
+        <v>2.090106798805076</v>
       </c>
       <c r="J18" t="n">
-        <v>4.73725678988186</v>
+        <v>4.692135393820992</v>
       </c>
       <c r="K18" t="n">
-        <v>19.89614806165107</v>
+        <v>16.04716691724328</v>
       </c>
       <c r="L18" t="n">
-        <v>43.50378038177587</v>
+        <v>44.82845783199407</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94501830178834</v>
+        <v>99.93038754290259</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.23286501009522</v>
+        <v>81.01125188895313</v>
       </c>
       <c r="C19" t="n">
-        <v>35.9280290486082</v>
+        <v>36.4358847212658</v>
       </c>
       <c r="D19" t="n">
-        <v>1.284553636105377</v>
+        <v>1.283315336449428</v>
       </c>
       <c r="E19" t="n">
-        <v>12.09320626262945</v>
+        <v>11.7502148442138</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584000790261839</v>
+        <v>0.7512800846558605</v>
       </c>
       <c r="G19" t="n">
-        <v>21.81267771233046</v>
+        <v>22.67720577373159</v>
       </c>
       <c r="H19" t="n">
-        <v>37.16733431719327</v>
+        <v>38.1107304918103</v>
       </c>
       <c r="I19" t="n">
-        <v>1.376692508896825</v>
+        <v>1.74300482899303</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740000493913648</v>
+        <v>4.695500529099127</v>
       </c>
       <c r="K19" t="n">
-        <v>20.76713498990476</v>
+        <v>18.98874811104687</v>
       </c>
       <c r="L19" t="n">
-        <v>43.25897277403431</v>
+        <v>44.51730864549828</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95413681254728</v>
+        <v>99.94194147781096</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.68457194661292</v>
+        <v>77.95291144068347</v>
       </c>
       <c r="C20" t="n">
-        <v>33.59175191951149</v>
+        <v>33.64575959480782</v>
       </c>
       <c r="D20" t="n">
-        <v>1.192128001542602</v>
+        <v>1.174138848285778</v>
       </c>
       <c r="E20" t="n">
-        <v>11.41438393191026</v>
+        <v>10.99281409393847</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587784705946365</v>
+        <v>0.751746997102645</v>
       </c>
       <c r="G20" t="n">
-        <v>20.243221581882</v>
+        <v>20.7479701311573</v>
       </c>
       <c r="H20" t="n">
-        <v>37.18587836316113</v>
+        <v>38.13441589860613</v>
       </c>
       <c r="I20" t="n">
-        <v>1.147816156305808</v>
+        <v>1.453406739701622</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742365441216477</v>
+        <v>4.698418731891531</v>
       </c>
       <c r="K20" t="n">
-        <v>23.31542805338708</v>
+        <v>22.04708855931654</v>
       </c>
       <c r="L20" t="n">
-        <v>43.05457856852095</v>
+        <v>44.25873504507029</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96175854141953</v>
+        <v>99.95158319919464</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.18822994166646</v>
+        <v>74.96240975877726</v>
       </c>
       <c r="C21" t="n">
-        <v>37.04094575196171</v>
+        <v>30.87803043575876</v>
       </c>
       <c r="D21" t="n">
-        <v>1.192893342765301</v>
+        <v>1.068037091503227</v>
       </c>
       <c r="E21" t="n">
-        <v>13.27094186123476</v>
+        <v>10.20141271924818</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592656032193976</v>
+        <v>0.7521520826907198</v>
       </c>
       <c r="G21" t="n">
-        <v>21.84162507797884</v>
+        <v>18.87306744498717</v>
       </c>
       <c r="H21" t="n">
-        <v>38.7951589745006</v>
+        <v>38.15496496943675</v>
       </c>
       <c r="I21" t="n">
-        <v>1.582935061846331</v>
+        <v>1.211824934094192</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745410020121234</v>
+        <v>4.700950516816998</v>
       </c>
       <c r="K21" t="n">
-        <v>17.81177005833354</v>
+        <v>25.03759024122274</v>
       </c>
       <c r="L21" t="n">
-        <v>45.09455354050084</v>
+        <v>44.04400691358234</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94726935079609</v>
+        <v>99.95962759056385</v>
       </c>
     </row>
   </sheetData>
